--- a/tools/data/gitapress_catalogue_vs_project.xlsx
+++ b/tools/data/gitapress_catalogue_vs_project.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6634ABB7-EC30-463F-BFA3-0CD25987C09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4EB433-AB07-4E08-A5C4-AD1559352D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8466" uniqueCount="1372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8466" uniqueCount="1373">
   <si>
     <t>क्र.</t>
   </si>
@@ -4139,6 +4139,9 @@
   </si>
   <si>
     <t xml:space="preserve"> है</t>
+  </si>
+  <si>
+    <t>Not required</t>
   </si>
 </sst>
 </file>
@@ -4165,7 +4168,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4189,6 +4192,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -4202,7 +4211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4215,6 +4224,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -39248,7 +39260,7 @@
         <v>89</v>
       </c>
       <c r="G388" s="2" t="s">
-        <v>257</v>
+        <v>458</v>
       </c>
       <c r="H388" s="2" t="s">
         <v>365</v>
@@ -39728,7 +39740,7 @@
         <v>89</v>
       </c>
       <c r="G403" s="2" t="s">
-        <v>257</v>
+        <v>458</v>
       </c>
       <c r="H403" s="2" t="s">
         <v>369</v>
@@ -39760,7 +39772,7 @@
         <v>89</v>
       </c>
       <c r="G404" s="2" t="s">
-        <v>257</v>
+        <v>458</v>
       </c>
       <c r="H404" s="2" t="s">
         <v>372</v>
@@ -40112,7 +40124,7 @@
         <v>89</v>
       </c>
       <c r="G415" s="2" t="s">
-        <v>257</v>
+        <v>1372</v>
       </c>
       <c r="H415" s="2" t="s">
         <v>374</v>
@@ -40188,17 +40200,17 @@
         <v>14</v>
       </c>
     </row>
-    <row r="418" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A418" s="2">
+    <row r="418" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A418" s="6">
         <v>417</v>
       </c>
-      <c r="B418" s="2">
+      <c r="B418" s="6">
         <v>1416</v>
       </c>
-      <c r="C418" s="2" t="s">
+      <c r="C418" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D418" s="2" t="s">
+      <c r="D418" s="6" t="s">
         <v>114</v>
       </c>
       <c r="E418" s="2">
@@ -40207,16 +40219,16 @@
       <c r="F418" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G418" s="2" t="s">
+      <c r="G418" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H418" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I418" s="2">
+      <c r="H418" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I418" s="6">
         <v>0.24</v>
       </c>
-      <c r="J418" s="2" t="s">
+      <c r="J418" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -40528,7 +40540,7 @@
         <v>117</v>
       </c>
       <c r="G428" s="2" t="s">
-        <v>257</v>
+        <v>458</v>
       </c>
       <c r="H428" s="2" t="s">
         <v>376</v>
